--- a/influencer_forms/020_playlist_promotion_contact_form--influencer_forms.xlsx
+++ b/influencer_forms/020_playlist_promotion_contact_form--influencer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -972,7 +972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hip-hop</t>
+          <t>reggae</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hip-Hop</t>
+          <t>Reggae</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>reggae</t>
+          <t>blues</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Reggae</t>
+          <t>Blues</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>blues</t>
+          <t>country-rock</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Blues</t>
+          <t>Country-Rock</t>
         </is>
       </c>
     </row>
@@ -1294,29 +1294,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>country-rock</t>
+          <t>electronic-dance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Country-Rock</t>
+          <t>Electronic-Dance</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>music_style_choices</t>
+          <t>music_genre_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>electronic-dance</t>
+          <t>hip-hop</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Electronic-Dance</t>
+          <t>Hip-Hop</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>hip-hop</t>
+          <t>r&amp;b</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hip-Hop</t>
+          <t>R&amp;B</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>r&amp;b</t>
+          <t>country</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>R&amp;B</t>
+          <t>Country</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>electronic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Electronic</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>electronic</t>
+          <t>pop</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Electronic</t>
+          <t>Pop</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>pop</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pop</t>
+          <t>Rock</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>rock</t>
+          <t>jazz</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rock</t>
+          <t>Jazz</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jazz</t>
+          <t>classical</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Classical</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>classical</t>
+          <t>reggae</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Classical</t>
+          <t>Reggae</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>reggae</t>
+          <t>blues</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Reggae</t>
+          <t>Blues</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>blues</t>
+          <t>folk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Blues</t>
+          <t>Folk</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>folk</t>
+          <t>rap</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Folk</t>
+          <t>Rap</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>rap</t>
+          <t>electronic-dance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rap</t>
+          <t>Electronic-Dance</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>electronic-dance</t>
+          <t>r&amp;b/pop</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Electronic-Dance</t>
+          <t>R&amp;B/Pop</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>r&amp;b/pop</t>
+          <t>rap/hip-hop</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>R&amp;B/Pop</t>
+          <t>Rap/Hip-Hop</t>
         </is>
       </c>
     </row>
@@ -1566,29 +1566,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>rap/hip-hop</t>
+          <t>country-rock</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rap/Hip-Hop</t>
+          <t>Country-Rock</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>music_genre_choices</t>
+          <t>playlist_type_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>country-rock</t>
+          <t>new_release</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Country-Rock</t>
+          <t>New Release</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>new_release</t>
+          <t>popular</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New Release</t>
+          <t>Popular</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>popular</t>
+          <t>up_and_coming</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Popular</t>
+          <t>Up and Coming</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>up_and_coming</t>
+          <t>editor's_pick</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Up and Coming</t>
+          <t>Editor's Pick</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>editor's_pick</t>
+          <t>user_created</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Editor's Pick</t>
+          <t>User Created</t>
         </is>
       </c>
     </row>
@@ -1668,29 +1668,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>user_created</t>
+          <t>featured</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>User Created</t>
+          <t>Featured</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>playlist_type_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>featured</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Featured</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1702,27 +1702,10 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
         <is>
           <t>No</t>
         </is>
